--- a/Lista_Obecnosci.xlsx
+++ b/Lista_Obecnosci.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uam-my.sharepoint.com/personal/matdra_amu_edu_pl1/Documents/Edukacja/C++/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uam-my.sharepoint.com/personal/matdra_amu_edu_pl1/Documents/Edukacja/C++/Pliki do edycji/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{42AD8775-372E-49F8-A521-6560A3323DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBF14684-83DD-4D70-AAEC-57F1A5AC7BF5}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{42AD8775-372E-49F8-A521-6560A3323DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C02245DE-E237-4090-B5F4-255F74EE7E5F}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{B02D29B5-B88A-4F42-86A3-8B720F5B597F}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="25">
   <si>
     <t>Skrót</t>
   </si>
@@ -89,6 +89,12 @@
   </si>
   <si>
     <t>Brak na liscie w USOS</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
 </sst>
 </file>
@@ -756,7 +762,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
@@ -788,6 +794,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -854,6 +863,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1260,7 +1273,9 @@
       <c r="D3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="5"/>
+      <c r="E3" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
@@ -1287,7 +1302,9 @@
       <c r="D4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
@@ -1314,7 +1331,9 @@
       <c r="D5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
@@ -1341,7 +1360,9 @@
       <c r="D6" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
@@ -1368,7 +1389,9 @@
       <c r="D7" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="5"/>
+      <c r="E7" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
@@ -1395,7 +1418,9 @@
       <c r="D8" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="5"/>
+      <c r="E8" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
@@ -1422,7 +1447,9 @@
       <c r="D9" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="5"/>
+      <c r="E9" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -1449,7 +1476,9 @@
       <c r="D10" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
@@ -1476,7 +1505,9 @@
       <c r="D11" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="5"/>
+      <c r="E11" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
@@ -1503,7 +1534,9 @@
       <c r="D12" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="5"/>
+      <c r="E12" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
@@ -1530,7 +1563,9 @@
       <c r="D13" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E13" s="5"/>
+      <c r="E13" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -1557,7 +1592,9 @@
       <c r="D14" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
@@ -1584,7 +1621,9 @@
       <c r="D15" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E15" s="5"/>
+      <c r="E15" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
@@ -1611,7 +1650,9 @@
       <c r="D16" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="5"/>
+      <c r="E16" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
@@ -1638,7 +1679,9 @@
       <c r="D17" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E17" s="5"/>
+      <c r="E17" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
@@ -1665,7 +1708,9 @@
       <c r="D18" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="1"/>
+      <c r="E18" s="19" t="s">
+        <v>24</v>
+      </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
